--- a/education_forms/049_teacher_administrative_support_assessment_form--education_forms.xlsx
+++ b/education_forms/049_teacher_administrative_support_assessment_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>communication_frequency</t>
+          <t>communication_frequency_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>communicationFrequency</t>
+          <t>Communication Frequency 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>communication_style</t>
+          <t>communication_style_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>communicationStyle</t>
+          <t>Communication Style 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>teacher_satisfaction</t>
+          <t>teacher_satisfaction_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>teacherSatisfaction</t>
+          <t>Teacher Satisfaction 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>communication_channels_used</t>
+          <t>communication_channels_used_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>communicationChannelsUsed</t>
+          <t>Communication Channels Used 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>communication_style_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>communication_style_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>communication_style_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_channels_used_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_channels_used_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_channels_used_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_channels_used_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>communication_channels_used_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
